--- a/inst/extdata/oq_small/OQ_Test2/OQ_Test2_Ab_Titration_Instructions.xlsx
+++ b/inst/extdata/oq_small/OQ_Test2/OQ_Test2_Ab_Titration_Instructions.xlsx
@@ -425,10 +425,10 @@
     <t>ScriptVersion</t>
   </si>
   <si>
-    <t>NOT ACTIVE as of v2_86 -- gate_manual is disabled in this version; use an automated gating method instead. Planned to return in a future ACTA release. (When active: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
-  </si>
-  <si>
-    <t>NOT ACTIVE as of v2_86 -- do not uncomment this row; gate_manual is disabled in this version. Planned to return in a future ACTA release.</t>
+    <t>NOT IMPLEMENTED -- use an automated gating method. Planned for a future release, not merely switched off: it needs an interactive gating UI that ACTA does not have, because flowGate's drawer launches its own blocking Shiny app and cannot run inside ACTA's. (Design intent: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
+  </si>
+  <si>
+    <t>NOT IMPLEMENTED -- do not uncomment this row. Drawing gates by hand needs an interactive gating UI that ACTA does not have; it is planned for a future release, not merely switched off. Use an automated method.</t>
   </si>
   <si>
     <t>flowjo_transformation_arg</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">gate_manual</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT ACTIVE as of v2_86 -- do not uncomment this row; gate_manual is disabled in this version. Planned to return in a future ACTA release.</t>
+    <t xml:space="preserve">NOT IMPLEMENTED -- do not uncomment this row. Drawing gates by hand needs an interactive gating UI that ACTA does not have; it is planned for a future release, not merely switched off. Use an automated method.</t>
   </si>
   <si>
     <t xml:space="preserve">#gate_flowclust_2d</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">(none -- gates come from the drawManualGates() cache; no tunable gating_args)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT ACTIVE as of v2_86 -- gate_manual is disabled in this version; use an automated gating method instead. Planned to return in a future ACTA release. (When active: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
+    <t xml:space="preserve">NOT IMPLEMENTED -- use an automated gating method. Planned for a future release, not merely switched off: it needs an interactive gating UI that ACTA does not have, because flowGate's drawer launches its own blocking Shiny app and cannot run inside ACTA's. (Design intent: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
   </si>
   <si>
     <t xml:space="preserve">dashboard_tabbed_by</t>
